--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488090_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488090_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6827</v>
+        <v>9.256500000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.984299999999999</v>
+        <v>7.5581</v>
       </c>
       <c r="F2" t="n">
         <v>1.6984</v>
@@ -610,10 +610,10 @@
         <v>2.7751</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2759</v>
+        <v>0.8498</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5955</v>
+        <v>1.1693</v>
       </c>
       <c r="U2" t="n">
         <v>-0.3196</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.6053</v>
+        <v>5.0084</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6808</v>
+        <v>2.4771</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9244</v>
+        <v>2.5313</v>
       </c>
       <c r="G3" t="n">
         <v>3.4975</v>
@@ -688,13 +688,13 @@
         <v>2.3787</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4447</v>
+        <v>0.8479</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6829</v>
+        <v>0.4792</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7618</v>
+        <v>0.3687</v>
       </c>
       <c r="V3" t="n">
         <v>0.2666</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. IBÁÑEZ FIDALGO</t>
+          <t>C. COBOS ORTEGA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4133</v>
+        <v>2.9273</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4133</v>
+        <v>1.765</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.1623</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4133</v>
+        <v>3.0017</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6052999999999999</v>
+        <v>2.1925</v>
       </c>
       <c r="I4" t="n">
-        <v>1.808</v>
+        <v>0.8093</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4133</v>
+        <v>3.3746</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6052999999999999</v>
+        <v>2.0449</v>
       </c>
       <c r="L4" t="n">
-        <v>1.808</v>
+        <v>1.3298</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-0.3729</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.1476</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.5205</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.9822</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.3727</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.447</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. COBOS ORTEGA</t>
+          <t>P. IBÁÑEZ FIDALGO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1196</v>
+        <v>2.4133</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1538</v>
+        <v>2.4133</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9657</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0017</v>
+        <v>2.4133</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1925</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8093</v>
+        <v>1.808</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3746</v>
+        <v>2.4133</v>
       </c>
       <c r="K5" t="n">
-        <v>2.0449</v>
+        <v>0.6052999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3298</v>
+        <v>1.808</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3729</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1476</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5205</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9822</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8821</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2386</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6435999999999999</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7575</v>
+        <v>2.3896</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9727</v>
+        <v>1.3802</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7848000000000001</v>
+        <v>1.0095</v>
       </c>
       <c r="G6" t="n">
         <v>2.4295</v>
@@ -922,13 +922,13 @@
         <v>0.9911</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4559</v>
+        <v>0.1762</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7488</v>
+        <v>-0.3413</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2928</v>
+        <v>0.5174</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2071</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4978</v>
+        <v>0.554</v>
       </c>
       <c r="E9" t="n">
         <v>1.9536</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4558</v>
+        <v>-1.3996</v>
       </c>
       <c r="G9" t="n">
         <v>0.5911999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>1.1893</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0161</v>
+        <v>-0.9599</v>
       </c>
       <c r="T9" t="n">
         <v>0.3047</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.3208</v>
+        <v>-1.2647</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2666</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0294</v>
+        <v>0.1561</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9152</v>
+        <v>1.3227</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8858</v>
+        <v>-1.1666</v>
       </c>
       <c r="G10" t="n">
         <v>0.7599</v>
@@ -1234,13 +1234,13 @@
         <v>2.3787</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0148</v>
+        <v>0.1119</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.444</v>
+        <v>-0.0365</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4292</v>
+        <v>0.1484</v>
       </c>
       <c r="V10" t="n">
         <v>0.8701</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. MUNOZ MENDOZA</t>
+          <t>J. RAMOS ANGULO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.8366</v>
+        <v>-0.6051</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9911</v>
+        <v>-0.2987</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1545</v>
+        <v>-0.3064</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4075</v>
+        <v>-0.8557</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4075</v>
+        <v>0.0148</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-0.8704</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6791</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6791</v>
+        <v>0.0069</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.0726</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2717</v>
+        <v>-0.79</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2717</v>
+        <v>0.0078</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9911</v>
+        <v>0.3964</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.3964</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5620000000000001</v>
+        <v>-0.1459</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6791</v>
+        <v>-0.233</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1171</v>
+        <v>0.0871</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. RAMOS ANGULO</t>
+          <t>J. VERKERK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.8369</v>
+        <v>-1.1529</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.5024</v>
+        <v>0.3875</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3345</v>
+        <v>-1.5404</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8557</v>
+        <v>0.5502</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0148</v>
+        <v>2.3888</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8704</v>
+        <v>-1.8386</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.06569999999999999</v>
+        <v>1.742</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0069</v>
+        <v>2.381</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.0726</v>
+        <v>-0.639</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.79</v>
+        <v>-1.1918</v>
       </c>
       <c r="N12" t="n">
         <v>0.0078</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-1.1996</v>
       </c>
       <c r="P12" t="n">
-        <v>0.3964</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3964</v>
+        <v>1.3876</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3777</v>
+        <v>0.3652</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4368</v>
+        <v>0.6278</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0591</v>
+        <v>-0.2625</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>J. MUNOZ MENDOZA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.1745</v>
+        <v>-1.216</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8591</v>
+        <v>-1.3986</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.0337</v>
+        <v>0.1826</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0076</v>
+        <v>-0.4075</v>
       </c>
       <c r="H13" t="n">
-        <v>0.905</v>
+        <v>-0.4075</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8974</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7951</v>
+        <v>-0.6791</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6344</v>
+        <v>-0.6791</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7875</v>
+        <v>0.2717</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7294</v>
+        <v>0.2717</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0581</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1982</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1893</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1733</v>
+        <v>0.1826</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0552</v>
+        <v>0.2717</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2284</v>
+        <v>-0.089</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. VERKERK</t>
+          <t>S. CASTRO BRAVO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.3213</v>
+        <v>-1.3419</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3875</v>
+        <v>-0.9335</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7089</v>
+        <v>-0.4084</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5502</v>
+        <v>-0.7191</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3888</v>
+        <v>-0.0915</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.8386</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>1.742</v>
+        <v>0.0805</v>
       </c>
       <c r="K14" t="n">
-        <v>2.381</v>
+        <v>0.0404</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.639</v>
+        <v>0.0402</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1918</v>
+        <v>-0.7996</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0078</v>
+        <v>-0.1319</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1996</v>
+        <v>-0.6677</v>
       </c>
       <c r="P14" t="n">
         <v>-0.5947</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1968</v>
+        <v>-0.7020999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6278</v>
+        <v>-0.0229</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.431</v>
+        <v>-0.6791</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.4737</v>
+        <v>0.674</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4737</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S. CASTRO BRAVO</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.4437</v>
+        <v>-1.5363</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.0354</v>
+        <v>0.5535</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4084</v>
+        <v>-2.0898</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.7191</v>
+        <v>0.0076</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0915</v>
+        <v>0.905</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.8974</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0805</v>
+        <v>1.7951</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0404</v>
+        <v>1.6344</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0402</v>
+        <v>0.1607</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7996</v>
+        <v>-1.7875</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1319</v>
+        <v>-0.7294</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6677</v>
+        <v>-1.0581</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.5947</v>
+        <v>0.1982</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.535</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1248</v>
+        <v>-0.2505</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6791</v>
+        <v>-0.2846</v>
       </c>
       <c r="V15" t="n">
-        <v>0.674</v>
+        <v>-1.2071</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.674</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.801</v>
+        <v>-5.1617</v>
       </c>
       <c r="E16" t="n">
-        <v>-4.6306</v>
+        <v>-4.0194</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1704</v>
+        <v>-1.1423</v>
       </c>
       <c r="G16" t="n">
         <v>-1.95</v>
@@ -1702,13 +1702,13 @@
         <v>1.784</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.6002</v>
+        <v>-0.9609</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3634</v>
+        <v>0.2479</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2368</v>
+        <v>-1.2087</v>
       </c>
       <c r="V16" t="n">
         <v>-0.0704</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>12.897</v>
+        <v>12.8967</v>
       </c>
       <c r="E17" t="n">
         <v>14.3662</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.469700000000001</v>
+        <v>-1.469400000000001</v>
       </c>
       <c r="G17" t="n">
         <v>13.8624</v>
@@ -1765,7 +1765,7 @@
         <v>-8.3866</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1569</v>
+        <v>0.1569000000000002</v>
       </c>
       <c r="O17" t="n">
         <v>-8.543600000000001</v>
@@ -1780,16 +1780,16 @@
         <v>16.8488</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8445999999999995</v>
+        <v>-0.8445999999999998</v>
       </c>
       <c r="T17" t="n">
-        <v>2.5888</v>
+        <v>2.5891</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.4335</v>
+        <v>-3.4336</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8700999999999998</v>
+        <v>0.8700999999999997</v>
       </c>
       <c r="W17" t="n">
         <v>7.368300000000001</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.2231</v>
+        <v>4.0109</v>
       </c>
       <c r="E18" t="n">
-        <v>5.4192</v>
+        <v>4.7061</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.196</v>
+        <v>-0.6952</v>
       </c>
       <c r="G18" t="n">
         <v>0.9004</v>
@@ -1858,13 +1858,13 @@
         <v>2.1805</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9263</v>
+        <v>0.714</v>
       </c>
       <c r="T18" t="n">
-        <v>1.865</v>
+        <v>1.1519</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9388</v>
+        <v>-0.4379</v>
       </c>
       <c r="V18" t="n">
         <v>1.2071</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.0656</v>
+        <v>3.479</v>
       </c>
       <c r="E19" t="n">
-        <v>4.8828</v>
+        <v>5.1884</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8171</v>
+        <v>-1.7094</v>
       </c>
       <c r="G19" t="n">
         <v>2.1647</v>
@@ -1936,13 +1936,13 @@
         <v>3.3698</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1435</v>
+        <v>0.2698</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2572</v>
+        <v>0.5628</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4007</v>
+        <v>-0.2929</v>
       </c>
       <c r="V19" t="n">
         <v>3.6213</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4954</v>
+        <v>-0.4249</v>
       </c>
       <c r="E22" t="n">
-        <v>1.7891</v>
+        <v>2.1966</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2845</v>
+        <v>-2.6215</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8256</v>
@@ -2170,13 +2170,13 @@
         <v>1.784</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2467</v>
+        <v>-0.1762</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7267</v>
+        <v>-0.3192</v>
       </c>
       <c r="U22" t="n">
-        <v>0.48</v>
+        <v>0.1431</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2071</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. REYES ORTEGA</t>
+          <t>L. MAERIEN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5732</v>
+        <v>-0.6983</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7467</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3199</v>
+        <v>-0.6137</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9145</v>
+        <v>-0.2275</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5433</v>
+        <v>-0.4036</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3712</v>
+        <v>0.176</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3375</v>
+        <v>0.0402</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3494</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.6869</v>
+        <v>0.0402</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.252</v>
+        <v>-0.2677</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1939</v>
+        <v>-0.4036</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0581</v>
+        <v>0.1358</v>
       </c>
       <c r="P23" t="n">
         <v>0.1982</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1893</v>
+        <v>0.1982</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0132</v>
+        <v>-0.1358</v>
       </c>
       <c r="T23" t="n">
-        <v>0.7967</v>
+        <v>-0.1248</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2165</v>
+        <v>-0.011</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8701</v>
+        <v>-0.5331</v>
       </c>
       <c r="W23" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4737</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>L. MAERIEN</t>
+          <t>J. REYES ORTEGA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.586</v>
+        <v>-0.777</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.08459999999999999</v>
+        <v>0.5429</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5014</v>
+        <v>-1.3199</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2275</v>
+        <v>-0.9145</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4036</v>
+        <v>-0.5433</v>
       </c>
       <c r="I24" t="n">
-        <v>0.176</v>
+        <v>-0.3712</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0402</v>
+        <v>0.3375</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>-0.3494</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0402</v>
+        <v>0.6869</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2677</v>
+        <v>-1.252</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4036</v>
+        <v>-0.1939</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1358</v>
+        <v>-1.0581</v>
       </c>
       <c r="P24" t="n">
         <v>0.1982</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1982</v>
+        <v>1.1893</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0235</v>
+        <v>0.8094</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1248</v>
+        <v>0.5929</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1013</v>
+        <v>0.2165</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5331</v>
+        <v>-0.8701</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.5331</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="25">
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>K. DOMINGOS</t>
+          <t>A. GUTIERREZ MORENO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.9201</v>
+        <v>-2.1304</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.8110000000000001</v>
+        <v>-1.118</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.1091</v>
+        <v>-1.0124</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4294</v>
+        <v>-1.1503</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.07530000000000001</v>
+        <v>-1.1905</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3541</v>
+        <v>0.0402</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4772</v>
+        <v>0.0604</v>
       </c>
       <c r="K26" t="n">
-        <v>0.3165</v>
+        <v>0.0202</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1607</v>
+        <v>0.0402</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.9066</v>
+        <v>-1.2107</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.3918</v>
+        <v>-1.2107</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.5148</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.1893</v>
+        <v>-0.7929</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R26" t="n">
-        <v>1.784</v>
+        <v>0.1982</v>
       </c>
       <c r="S26" t="n">
-        <v>1.3131</v>
+        <v>-0.1872</v>
       </c>
       <c r="T26" t="n">
-        <v>2.0925</v>
+        <v>-0.1872</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.7794</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.6145</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.4074</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MORENO</t>
+          <t>K. DOMINGOS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.1304</v>
+        <v>-2.5045</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.118</v>
+        <v>-1.7278</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.0124</v>
+        <v>-0.7766999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.1503</v>
+        <v>-0.4294</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.1905</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0402</v>
+        <v>-0.3541</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0604</v>
+        <v>0.4772</v>
       </c>
       <c r="K27" t="n">
-        <v>0.0202</v>
+        <v>0.3165</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0402</v>
+        <v>0.1607</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.2107</v>
+        <v>-0.9066</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.2107</v>
+        <v>-0.3918</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>-0.5148</v>
       </c>
       <c r="P27" t="n">
-        <v>-0.7929</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R27" t="n">
-        <v>0.1982</v>
+        <v>1.784</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.1872</v>
+        <v>0.7287</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1872</v>
+        <v>1.1757</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>-0.447</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>-1.6145</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>-0.4074</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-6.895</v>
+        <v>-5.969</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.9814</v>
+        <v>-2.472</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.9136</v>
+        <v>-3.497</v>
       </c>
       <c r="G28" t="n">
         <v>-6.6636</v>
@@ -2638,13 +2638,13 @@
         <v>3.568</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.947</v>
+        <v>-0.021</v>
       </c>
       <c r="T28" t="n">
-        <v>0.0076</v>
+        <v>0.5169</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.9546</v>
+        <v>-0.538</v>
       </c>
       <c r="V28" t="n">
         <v>-0.8701</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-7.9855</v>
+        <v>-7.6035</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.5786</v>
+        <v>-6.9674</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4069</v>
+        <v>-0.6361</v>
       </c>
       <c r="G29" t="n">
         <v>-7.7201</v>
@@ -2716,13 +2716,13 @@
         <v>3.568</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.8601</v>
+        <v>-0.4781</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.5468</v>
+        <v>0.0645</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.3133</v>
+        <v>-0.5425</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-12.8968</v>
+        <v>-12.2176</v>
       </c>
       <c r="E30" t="n">
         <v>1.469600000000002</v>
       </c>
       <c r="F30" t="n">
-        <v>-14.3662</v>
+        <v>-13.6872</v>
       </c>
       <c r="G30" t="n">
         <v>-13.8623</v>
@@ -2770,7 +2770,7 @@
         <v>8.386699999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.1570000000000011</v>
+        <v>-0.1570000000000003</v>
       </c>
       <c r="L30" t="n">
         <v>8.543800000000003</v>
@@ -2794,16 +2794,16 @@
         <v>17.84</v>
       </c>
       <c r="S30" t="n">
-        <v>0.8446000000000004</v>
+        <v>1.5236</v>
       </c>
       <c r="T30" t="n">
         <v>3.4335</v>
       </c>
       <c r="U30" t="n">
-        <v>-2.589</v>
+        <v>-1.9097</v>
       </c>
       <c r="V30" t="n">
-        <v>-0.8700999999999995</v>
+        <v>-0.8701</v>
       </c>
       <c r="W30" t="n">
         <v>6.4983</v>
